--- a/documents/shenzhen_air/标签单.xlsx
+++ b/documents/shenzhen_air/标签单.xlsx
@@ -11,9 +11,6 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$D$4</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
